--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.489292922639819</v>
+        <v>1.054510099928971</v>
       </c>
       <c r="D2" t="n">
-        <v>4.13496895252898</v>
+        <v>0.6719324547859593</v>
       </c>
       <c r="E2" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F2" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.96370966636911</v>
+        <v>7.144102820784981</v>
       </c>
       <c r="D3" t="n">
-        <v>50.10352394038499</v>
+        <v>8.141822640312562</v>
       </c>
       <c r="E3" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F3" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.38475297356175</v>
+        <v>4.937522358203784</v>
       </c>
       <c r="D4" t="n">
-        <v>42.23862711311243</v>
+        <v>6.86377690588077</v>
       </c>
       <c r="E4" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F4" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.17123424654296</v>
+        <v>4.74032556506323</v>
       </c>
       <c r="D5" t="n">
-        <v>26.88838960962131</v>
+        <v>4.369363311563464</v>
       </c>
       <c r="E5" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F5" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.75442528625071</v>
+        <v>5.81009410901574</v>
       </c>
       <c r="D6" t="n">
-        <v>41.23538585871044</v>
+        <v>6.700750202040446</v>
       </c>
       <c r="E6" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F6" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.80065037135141</v>
+        <v>4.192605685344604</v>
       </c>
       <c r="D7" t="n">
-        <v>28.988560377481</v>
+        <v>4.710641061340663</v>
       </c>
       <c r="E7" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F7" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.99714121991953</v>
+        <v>5.687035448236925</v>
       </c>
       <c r="D8" t="n">
-        <v>45.76568220930869</v>
+        <v>7.436923359012662</v>
       </c>
       <c r="E8" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F8" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.87029782770993</v>
+        <v>2.903923397002864</v>
       </c>
       <c r="D9" t="n">
-        <v>41.23649755123785</v>
+        <v>6.700930852076151</v>
       </c>
       <c r="E9" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F9" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.23075455056003</v>
+        <v>2.474997614466006</v>
       </c>
       <c r="D10" t="n">
-        <v>34.99233470345187</v>
+        <v>5.68625438931093</v>
       </c>
       <c r="E10" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F10" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.33225938102408</v>
+        <v>2.328992149416413</v>
       </c>
       <c r="D11" t="n">
-        <v>76.84180998239479</v>
+        <v>12.48679412213915</v>
       </c>
       <c r="E11" t="n">
-        <v>11.06065431715014</v>
+        <v>1.797356326536897</v>
       </c>
       <c r="F11" t="n">
-        <v>17.60544296186822</v>
+        <v>2.860884481303586</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
